--- a/data/trans_bre/P1410-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1410-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,04</t>
+          <t>-2,41</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-42,41%</t>
+          <t>-45,68%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,04; -0,98</t>
+          <t>-5,74; -0,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,11; -0,74</t>
+          <t>-4,17; -0,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 3,76</t>
+          <t>-2,0; 3,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,13; -0,02</t>
+          <t>-4,57; -0,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-92,41; -7,19</t>
+          <t>-92,43; -13,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 21,73</t>
+          <t>-100,0; -17,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-45,51; 195,23</t>
+          <t>-49,49; 200,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-67,31; 2,26</t>
+          <t>-69,84; -5,04</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,87</t>
+          <t>-2,9</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-68,81%</t>
+          <t>-69,84%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 0,44</t>
+          <t>-4,17; 0,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,34</t>
+          <t>-3,92; 0,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 0,15</t>
+          <t>-4,33; 0,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,8; -1,14</t>
+          <t>-4,9; -1,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-85,89; 43,85</t>
+          <t>-85,43; 58,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-92,52; 73,09</t>
+          <t>-100,0; 73,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-84,62; 19,96</t>
+          <t>-85,97; 27,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-87,51; -32,58</t>
+          <t>-89,53; -38,95</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,02</t>
+          <t>-0,15</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>-2,31%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 0,13</t>
+          <t>-5,05; 0,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 2,22</t>
+          <t>-3,72; 2,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 8,95</t>
+          <t>-1,1; 8,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 9,79</t>
+          <t>-3,66; 5,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 18,73</t>
+          <t>-90,14; 28,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-65,87; 60,52</t>
+          <t>-65,59; 66,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-24,44; 240,68</t>
+          <t>-26,76; 256,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-32,72; 404,89</t>
+          <t>-52,44; 96,78</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-4,17</t>
+          <t>-3,59</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-67,01%</t>
+          <t>-59,14%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,0; -0,16</t>
+          <t>-4,08; -0,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,84; -0,62</t>
+          <t>-3,99; -0,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,13</t>
+          <t>-3,22; 0,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,1; -2,54</t>
+          <t>-5,02; -2,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,91; -1,8</t>
+          <t>-62,05; -5,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,08; -16,04</t>
+          <t>-75,25; -17,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-64,53; 5,13</t>
+          <t>-62,82; 4,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-85,18; -48,11</t>
+          <t>-72,81; -38,47</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,47</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-21,04%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 2,59</t>
+          <t>-3,17; 2,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 4,53</t>
+          <t>-0,61; 4,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 2,4</t>
+          <t>-2,1; 2,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 1,0</t>
+          <t>-2,1; 2,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-50,13; 80,85</t>
+          <t>-47,68; 82,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 134,3</t>
+          <t>-11,19; 126,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-38,6; 80,98</t>
+          <t>-40,36; 62,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-48,76; 18,89</t>
+          <t>-27,42; 48,33</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,74</t>
+          <t>4,9</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>212,27%</t>
+          <t>251,11%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,18; 5,77</t>
+          <t>3,2; 5,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,24; 6,14</t>
+          <t>1,31; 6,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,49; 8,23</t>
+          <t>4,48; 8,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 7,21</t>
+          <t>-1,45; 7,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,81; 1457,67</t>
+          <t>18,0; 1597,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,7; 3268,17</t>
+          <t>-25,28; 2795,65</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,03</t>
+          <t>-0,96</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-20,03%</t>
+          <t>-17,71%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,12</t>
+          <t>-1,8; 0,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,28</t>
+          <t>-0,74; 1,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,83</t>
+          <t>-0,16; 1,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 0,36</t>
+          <t>-1,91; -0,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-34,89; 2,78</t>
+          <t>-36,22; 3,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,46; 36,85</t>
+          <t>-16,31; 34,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 55,25</t>
+          <t>-3,97; 52,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-36,86; 7,44</t>
+          <t>-32,29; -2,57</t>
         </is>
       </c>
     </row>
